--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>137215864</v>
       </c>
       <c r="B20" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137215880</v>
       </c>
       <c r="B21" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>137216824</v>
       </c>
       <c r="B22" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137216163</v>
       </c>
       <c r="B23" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>137215864</v>
       </c>
       <c r="B20" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137215880</v>
       </c>
       <c r="B21" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>137216824</v>
       </c>
       <c r="B22" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137216163</v>
       </c>
       <c r="B23" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -2657,11 +2657,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyrberget, Ång</t>
@@ -2764,11 +2760,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyrberget, Ång</t>
@@ -2875,11 +2867,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stormyrberget, Ång</t>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>137215864</v>
       </c>
       <c r="B20" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137215880</v>
       </c>
       <c r="B21" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137216824</v>
       </c>
       <c r="B22" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>137216163</v>
       </c>
       <c r="B23" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>137215864</v>
       </c>
       <c r="B20" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137215880</v>
       </c>
       <c r="B21" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137216824</v>
       </c>
       <c r="B22" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>137216163</v>
       </c>
       <c r="B23" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>137215864</v>
       </c>
       <c r="B20" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137215880</v>
       </c>
       <c r="B21" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137216824</v>
       </c>
       <c r="B22" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>137216163</v>
       </c>
       <c r="B23" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22062-2026 artfynd.xlsx
+++ b/artfynd/A 22062-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137217641</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137215747</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137215976</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137216968</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137217334</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137217612</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137217722</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137217757</v>
       </c>
       <c r="B9" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137215992</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137217598</v>
       </c>
       <c r="B11" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137216933</v>
       </c>
       <c r="B12" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137215961</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137216097</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137216449</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>137216804</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>137216510</v>
       </c>
       <c r="B17" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>137216693</v>
       </c>
       <c r="B18" t="n">
-        <v>80654</v>
+        <v>80658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137216516</v>
       </c>
       <c r="B19" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>137215864</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>137215880</v>
       </c>
       <c r="B21" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137216824</v>
       </c>
       <c r="B22" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>137216163</v>
       </c>
       <c r="B23" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>137215758</v>
       </c>
       <c r="B24" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137216047</v>
       </c>
       <c r="B25" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137216073</v>
       </c>
       <c r="B26" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
